--- a/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_icc_test_250410.xlsx
+++ b/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_icc_test_250410.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12_PWM_Rev_1\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B127856-9065-42FE-97FB-A65C22A985DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4951A9-CC12-4641-9BB4-D13A014317F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="5760" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ICC" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="58">
   <si>
     <t>ICC</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -180,6 +181,107 @@
   <si>
     <t>IOUT OFF (Stanby)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>input</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000-2</t>
+  </si>
+  <si>
+    <t>4000-3</t>
+  </si>
+  <si>
+    <t>4000-4</t>
+  </si>
+  <si>
+    <t>4000-5</t>
+  </si>
+  <si>
+    <t>4000-6</t>
+  </si>
+  <si>
+    <t>4000-7</t>
+  </si>
+  <si>
+    <t>4000-8</t>
+  </si>
+  <si>
+    <t>4000-9</t>
+  </si>
+  <si>
+    <t>4000-10</t>
+  </si>
+  <si>
+    <t>4001-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4001-2</t>
+  </si>
+  <si>
+    <t>4001-3</t>
+  </si>
+  <si>
+    <t>4001-4</t>
+  </si>
+  <si>
+    <t>4001-5</t>
+  </si>
+  <si>
+    <t>4001-6</t>
+  </si>
+  <si>
+    <t>4001-7</t>
+  </si>
+  <si>
+    <t>4001-8</t>
+  </si>
+  <si>
+    <t>4001-9</t>
+  </si>
+  <si>
+    <t>4001-10</t>
+  </si>
+  <si>
+    <t>4002-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4002-2</t>
+  </si>
+  <si>
+    <t>4002-3</t>
+  </si>
+  <si>
+    <t>4002-4</t>
+  </si>
+  <si>
+    <t>4002-5</t>
+  </si>
+  <si>
+    <t>4002-6</t>
+  </si>
+  <si>
+    <t>4002-7</t>
+  </si>
+  <si>
+    <t>4002-8</t>
+  </si>
+  <si>
+    <t>4002-9</t>
+  </si>
+  <si>
+    <t>4002-10</t>
   </si>
 </sst>
 </file>
@@ -619,7 +721,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -693,6 +795,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -705,18 +840,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -724,12 +850,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -738,12 +858,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -771,18 +885,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -798,6 +901,1473 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11877341898210664"/>
+          <c:y val="0.11142022209234366"/>
+          <c:w val="0.8465961487640753"/>
+          <c:h val="0.77692982415771961"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>4000</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$B$3:$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4000-1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4000-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4000-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4000-6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4000-7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4000-8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4000-9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4000-10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$3:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3999.258476232008</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3999.5266334063567</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3999.5957982641262</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3999.6354293975787</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3999.7677197212797</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3999.839496980831</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3999.8653479761851</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4000.2297938343709</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4000.4447107268243</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4000.5570748546584</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A625-4891-BE85-16BB029CF756}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>4001</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$B$13:$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4001-10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4001-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4001-1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4001-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4001-7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4001-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4001-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4001-5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4001-8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4001-9</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$13:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4000.0111393536617</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4000.0900916391497</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4000.2212110879213</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000.244588423182</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4000.3173864462897</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4001.071106422919</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4001.305715690065</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4001.8062978800413</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4001.9521901974808</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4001.996828182997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A625-4891-BE85-16BB029CF756}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>4002</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$B$23:$B$32</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4002-7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4002-9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4002-8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4002-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4002-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4002-10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4002-5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4002-6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4002-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4002-1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$23:$C$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4001.3639439486242</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4001.3867418526502</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4001.6901364119635</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4001.8261576603786</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4001.879065535873</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4002.1209211984947</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4002.6428186092794</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4002.837630977172</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4002.8667586667398</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4002.8736699580254</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A625-4891-BE85-16BB029CF756}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="179532719"/>
+        <c:axId val="179525039"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="179532719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="179525039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="179525039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="179532719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.87441130730897076"/>
+          <c:y val="1.349894384183859E-2"/>
+          <c:w val="8.3334082721421718E-2"/>
+          <c:h val="8.5623271375122545E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="241">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>322264</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="차트 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{161EB2EA-DD9D-495A-AFC1-E8DDC262D34F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1064,37 +2634,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{067F9B3C-4F59-4680-86CB-4ABF86107B5C}">
   <dimension ref="B2:N30"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="23.4375" customWidth="1"/>
-    <col min="5" max="7" width="12.9375" customWidth="1"/>
-    <col min="8" max="20" width="12.6875" customWidth="1"/>
+    <col min="4" max="4" width="23.4140625" customWidth="1"/>
+    <col min="5" max="7" width="12.9140625" customWidth="1"/>
+    <col min="8" max="20" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65"/>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B3" s="29" t="s">
+    <row r="2" spans="2:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="30"/>
-    </row>
-    <row r="4" spans="2:8" ht="26.65" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="35"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="40"/>
+    </row>
+    <row r="4" spans="2:8" ht="26.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B4" s="41"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="43"/>
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1108,26 +2678,26 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B5" s="42" t="s">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="49" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="28">
         <v>0.85</v>
       </c>
-      <c r="F5" s="41"/>
+      <c r="F5" s="29"/>
       <c r="G5" s="5"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B6" s="43"/>
-      <c r="C6" s="46"/>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B6" s="47"/>
+      <c r="C6" s="50"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
@@ -1140,9 +2710,9 @@
       <c r="G6" s="10"/>
       <c r="H6" s="11"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B7" s="43"/>
-      <c r="C7" s="46"/>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B7" s="47"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="12" t="s">
         <v>12</v>
       </c>
@@ -1155,9 +2725,9 @@
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B8" s="43"/>
-      <c r="C8" s="46"/>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B8" s="47"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="7" t="s">
         <v>13</v>
       </c>
@@ -1170,9 +2740,9 @@
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B9" s="43"/>
-      <c r="C9" s="46"/>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B9" s="47"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="7" t="s">
         <v>14</v>
       </c>
@@ -1185,9 +2755,9 @@
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B10" s="43"/>
-      <c r="C10" s="46"/>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B10" s="47"/>
+      <c r="C10" s="50"/>
       <c r="D10" s="12" t="s">
         <v>15</v>
       </c>
@@ -1200,9 +2770,9 @@
       <c r="G10" s="10"/>
       <c r="H10" s="11"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B11" s="43"/>
-      <c r="C11" s="46"/>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B11" s="47"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="7" t="s">
         <v>16</v>
       </c>
@@ -1215,9 +2785,9 @@
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B12" s="43"/>
-      <c r="C12" s="46"/>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B12" s="47"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="12" t="s">
         <v>17</v>
       </c>
@@ -1230,9 +2800,9 @@
       <c r="G12" s="10"/>
       <c r="H12" s="11"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B13" s="43"/>
-      <c r="C13" s="47"/>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B13" s="47"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="7" t="s">
         <v>18</v>
       </c>
@@ -1245,48 +2815,48 @@
       <c r="G13" s="10"/>
       <c r="H13" s="11"/>
     </row>
-    <row r="14" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B14" s="44"/>
+    <row r="14" spans="2:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B14" s="48"/>
       <c r="C14" s="13" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="14"/>
-      <c r="E14" s="36">
+      <c r="E14" s="30">
         <v>0.3</v>
       </c>
-      <c r="F14" s="37"/>
+      <c r="F14" s="31"/>
       <c r="G14" s="15"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B15" s="38" t="s">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B15" s="44" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="4"/>
-      <c r="E15" s="40">
+      <c r="E15" s="28">
         <v>0.6</v>
       </c>
-      <c r="F15" s="41"/>
+      <c r="F15" s="29"/>
       <c r="G15" s="5"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B16" s="39"/>
+    <row r="16" spans="2:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B16" s="45"/>
       <c r="C16" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="14"/>
-      <c r="E16" s="36">
+      <c r="E16" s="30">
         <v>1</v>
       </c>
-      <c r="F16" s="37"/>
+      <c r="F16" s="31"/>
       <c r="G16" s="15"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="17" spans="2:14" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -1295,25 +2865,25 @@
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.6">
-      <c r="B18" s="29"/>
-      <c r="C18" s="25" t="s">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B18" s="32"/>
+      <c r="C18" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="30"/>
-    </row>
-    <row r="19" spans="2:14" ht="26.65" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B19" s="54"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="28"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="40"/>
+    </row>
+    <row r="19" spans="2:14" ht="26.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B19" s="33"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="39"/>
       <c r="E19" s="1" t="s">
         <v>4</v>
       </c>
@@ -1339,37 +2909,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.6">
-      <c r="B20" s="48" t="s">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B20" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="51" t="s">
+      <c r="C20" s="25" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="28">
         <f>E5+$E$14+$E$15</f>
         <v>1.75</v>
       </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="31">
+      <c r="F20" s="29"/>
+      <c r="G20" s="34">
         <v>3.2</v>
       </c>
-      <c r="H20" s="32"/>
-      <c r="J20" s="31">
+      <c r="H20" s="35"/>
+      <c r="J20" s="34">
         <v>3.153</v>
       </c>
-      <c r="K20" s="32"/>
-      <c r="M20" s="31">
+      <c r="K20" s="35"/>
+      <c r="M20" s="34">
         <v>3.2</v>
       </c>
-      <c r="N20" s="32"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.6">
-      <c r="B21" s="49"/>
-      <c r="C21" s="52"/>
+      <c r="N20" s="35"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B21" s="53"/>
+      <c r="C21" s="26"/>
       <c r="D21" s="7" t="s">
         <v>11</v>
       </c>
@@ -1400,9 +2970,9 @@
         <v>3.222</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.6">
-      <c r="B22" s="49"/>
-      <c r="C22" s="52"/>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B22" s="53"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="7" t="s">
         <v>12</v>
       </c>
@@ -1433,9 +3003,9 @@
         <v>3.3450000000000002</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.6">
-      <c r="B23" s="49"/>
-      <c r="C23" s="52"/>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B23" s="53"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="7" t="s">
         <v>13</v>
       </c>
@@ -1466,9 +3036,9 @@
         <v>3.4740000000000002</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.6">
-      <c r="B24" s="49"/>
-      <c r="C24" s="52"/>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B24" s="53"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="7" t="s">
         <v>14</v>
       </c>
@@ -1499,9 +3069,9 @@
         <v>3.6040000000000001</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.6">
-      <c r="B25" s="49"/>
-      <c r="C25" s="52"/>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B25" s="53"/>
+      <c r="C25" s="26"/>
       <c r="D25" s="7" t="s">
         <v>15</v>
       </c>
@@ -1532,9 +3102,9 @@
         <v>3.8730000000000002</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.6">
-      <c r="B26" s="49"/>
-      <c r="C26" s="52"/>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B26" s="53"/>
+      <c r="C26" s="26"/>
       <c r="D26" s="7" t="s">
         <v>16</v>
       </c>
@@ -1565,9 +3135,9 @@
         <v>4.1360000000000001</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.6">
-      <c r="B27" s="49"/>
-      <c r="C27" s="52"/>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B27" s="53"/>
+      <c r="C27" s="26"/>
       <c r="D27" s="7" t="s">
         <v>17</v>
       </c>
@@ -1598,9 +3168,9 @@
         <v>4.633</v>
       </c>
     </row>
-    <row r="28" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B28" s="50"/>
-      <c r="C28" s="53"/>
+    <row r="28" spans="2:14" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B28" s="54"/>
+      <c r="C28" s="27"/>
       <c r="D28" s="14" t="s">
         <v>18</v>
       </c>
@@ -1631,20 +3201,11 @@
         <v>5.2329999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.45">
       <c r="D30" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C20:C28"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="J20:K20"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
@@ -1657,8 +3218,280 @@
     <mergeCell ref="C5:C13"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B20:B28"/>
+    <mergeCell ref="C20:C28"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="J20:K20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA3A57B-3069-43D0-9DEA-B85DAA59E243}">
+  <dimension ref="B2:C32"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B3" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>3999.258476232008</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B4" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>3999.5266334063567</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B5" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>3999.5957982641262</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B6" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>3999.6354293975787</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B7" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>3999.7677197212797</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B8" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>3999.839496980831</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B9" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <v>3999.8653479761851</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B10" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>4000.2297938343709</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B11" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11">
+        <v>4000.4447107268243</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B12" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12">
+        <v>4000.5570748546584</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B13" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13">
+        <v>4000.0111393536617</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B14" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14">
+        <v>4000.0900916391497</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B15" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <v>4000.2212110879213</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B16" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>4000.244588423182</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B17" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>4000.3173864462897</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B18" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18">
+        <v>4001.071106422919</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B19" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19">
+        <v>4001.305715690065</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B20" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20">
+        <v>4001.8062978800413</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B21" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21">
+        <v>4001.9521901974808</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B22" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22">
+        <v>4001.996828182997</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B23" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23">
+        <v>4001.3639439486242</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B24" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24">
+        <v>4001.3867418526502</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B25" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25">
+        <v>4001.6901364119635</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B26" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26">
+        <v>4001.8261576603786</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B27" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27">
+        <v>4001.879065535873</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B28" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28">
+        <v>4002.1209211984947</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B29" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29">
+        <v>4002.6428186092794</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B30" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30">
+        <v>4002.837630977172</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B31" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31">
+        <v>4002.8667586667398</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B32" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32">
+        <v>4002.8736699580254</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B23:C32">
+    <sortCondition ref="C23:C32"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>